--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0003T0006Z000C1N8_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0003T0006Z000C1N8_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>60.08361779738929</v>
+        <v>9.76358789207576</v>
       </c>
       <c r="D2" t="n">
-        <v>56.90349283797911</v>
+        <v>9.246817586171606</v>
       </c>
       <c r="E2" t="n">
-        <v>6.979373313269083</v>
+        <v>1.134148163406226</v>
       </c>
       <c r="F2" t="n">
-        <v>9.178348653983594</v>
+        <v>1.491481656272334</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>75.20666615253164</v>
+        <v>12.22108324978639</v>
       </c>
       <c r="D3" t="n">
-        <v>44.26341604530766</v>
+        <v>7.192805107362496</v>
       </c>
       <c r="E3" t="n">
-        <v>6.979373313269083</v>
+        <v>1.134148163406226</v>
       </c>
       <c r="F3" t="n">
-        <v>9.178348653983594</v>
+        <v>1.491481656272334</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>74.54966872506409</v>
+        <v>12.11432116782292</v>
       </c>
       <c r="D4" t="n">
-        <v>34.48187929913333</v>
+        <v>5.603305386109167</v>
       </c>
       <c r="E4" t="n">
-        <v>6.979373313269083</v>
+        <v>1.134148163406226</v>
       </c>
       <c r="F4" t="n">
-        <v>9.178348653983594</v>
+        <v>1.491481656272334</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
